--- a/Тест2/212.xlsx
+++ b/Тест2/212.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="77">
   <si>
     <t xml:space="preserve">Question</t>
   </si>
@@ -171,16 +171,16 @@
     <t xml:space="preserve">Leptospirozda buyrak, mushak belgisi ko'p</t>
   </si>
   <si>
-    <t xml:space="preserve">Ikkalasida sariqlik umuman yo'q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gepatitda mushak og'rig'i kuchli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikkalasida jigar fermenti normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gepatitda buyrak belgisi ko'proq</t>
+    <t xml:space="preserve">Ikkalasida sariqlik umuman bo'lmaydi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gepatitda mushak og'rig'i kuchli bo'ladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikkalasida jigar fermenti normal bo'ladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gepatitda buyrak belgisi ko'proq bo'ladi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Leptospirozda buyrak, mushak belgisi ko'p. Sariqlik va jigar fermentlari ko'rsatkichlari muhim, ammo leptospirozda buyrak va mushak belgilari ko'proq namoyon bo'ladi. Manba: Mavzu materiali (212.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
@@ -210,10 +210,13 @@
     <t xml:space="preserve">Dastlabki kunlarda qaysi usullar ustun?</t>
   </si>
   <si>
-    <t xml:space="preserve">Siydik kulturasi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAT va ELISA</t>
+    <t xml:space="preserve">Siydik kulturasi usuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAT va ELISA tahlili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gram bo'yash usuli</t>
   </si>
   <si>
     <t xml:space="preserve">PCR va qon kulturasi</t>
@@ -865,7 +868,7 @@
         <v>57</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>58</v>
@@ -874,68 +877,68 @@
         <v>59</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
